--- a/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen bornquitis crónica</t>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,96</t>
+          <t>1,36; 11,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,57</t>
+          <t>1,15; 6,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,31</t>
+          <t>0,4; 4,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,74</t>
+          <t>0,6; 6,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,56</t>
+          <t>0,6; 5,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,63</t>
+          <t>0,56; 4,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,91</t>
+          <t>1,14; 6,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,51</t>
+          <t>0,41; 3,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,13</t>
+          <t>0,88; 4,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,63</t>
+          <t>0,6; 3,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,93</t>
+          <t>0,14; 2,11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,75</t>
+          <t>0,91; 7,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,62</t>
+          <t>0,98; 5,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,74</t>
+          <t>0,69; 6,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,12</t>
+          <t>0,76; 7,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,6</t>
+          <t>0,56; 4,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,6</t>
+          <t>0,4; 3,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,76</t>
+          <t>1,44; 12,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 21,66</t>
+          <t>5,11; 20,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,03</t>
+          <t>0,72; 6,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,36</t>
+          <t>2,69; 12,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,01</t>
+          <t>1,18; 9,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,86</t>
+          <t>0,67; 6,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1561,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,25</t>
+          <t>0,48; 4,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,5</t>
+          <t>1,72; 7,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,16</t>
+          <t>0,45; 4,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,68</t>
+          <t>2,4; 11,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,54</t>
+          <t>0,72; 3,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,13</t>
+          <t>0,23; 2,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,01</t>
+          <t>2,7; 7,81</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,43</t>
+          <t>0,48; 4,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,49</t>
+          <t>0,37; 3,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,97</t>
+          <t>0,86; 5,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,5</t>
+          <t>0,73; 4,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,86</t>
+          <t>1,14; 3,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,15</t>
+          <t>0,78; 3,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,2</t>
+          <t>0,73; 2,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,5</t>
+          <t>0,84; 2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,84</t>
+          <t>0,57; 1,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,33</t>
+          <t>0,7; 2,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,12</t>
+          <t>0,61; 1,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,23</t>
+          <t>0,8; 2,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,53</t>
+          <t>0,77; 2,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,85; 1,95</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,67</t>
+          <t>1,45; 2,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,77</t>
+          <t>0,84; 1,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,01</t>
+          <t>0,81; 1,99</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3520</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3512</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>719; 6271</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4119</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3923</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4995</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1308; 7781</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>483; 4988</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5439</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3826</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3154</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>631; 6305</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3181</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4910</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>651; 6265</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>623; 5167</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1256; 7033</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2734</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>867; 6957</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1900; 8841</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1279; 7661</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>361; 5360</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4945</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3532</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3469</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>643; 5430</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1358; 7734</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3046</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>520; 5167</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3795</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6119</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4621</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>627; 5871</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3782</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>859; 6733</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>635; 5961</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5302</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5516</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2601</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>603; 5069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4556</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4263</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3647</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2357; 9433</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>624; 5966</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2417; 10861</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4387</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3909</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3908</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3107</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>712; 5976</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5538</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3076</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3546</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>777; 7431</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4229</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2941</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4773</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2299</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8458</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>13231</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3372</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>667; 6016</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4595</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2142; 9645</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3420</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>660; 6420</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4723</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3739; 17505</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5282</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2038; 9839</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>652; 5952</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>7563; 21901</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3072</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7138</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5660</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>765; 6891</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>600; 5678</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4720</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1416; 8914</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3934</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1247; 7885</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3668; 11692</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3850</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2629; 10072</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5013</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>18105</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>4955; 14993</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5958; 17024</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3992; 12658</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4649; 14870</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4393; 13975</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>12635; 27606</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5957; 16412</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>5837; 18656</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>11998; 27440</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>21118; 38755</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>12131; 25866</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>11584; 28318</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,84</t>
+          <t>1,56; 12,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,84</t>
+          <t>1,19; 7,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,09</t>
+          <t>0,41; 4,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,02</t>
+          <t>0,61; 6,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,76</t>
+          <t>0,6; 5,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,65</t>
+          <t>0,56; 4,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,38</t>
+          <t>1,13; 6,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,31</t>
+          <t>0,32; 3,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,1</t>
+          <t>0,86; 3,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,58</t>
+          <t>0,87; 4,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,11</t>
+          <t>0,13; 2,01</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,69</t>
+          <t>0,91; 8,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,57</t>
+          <t>0,96; 5,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,9</t>
+          <t>0,69; 7,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,14</t>
+          <t>0,77; 6,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,37</t>
+          <t>0,54; 4,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,73</t>
+          <t>0,39; 4,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,11</t>
+          <t>1,44; 10,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,81</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 20,46</t>
+          <t>4,75; 21,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,88</t>
+          <t>0,73; 6,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,07</t>
+          <t>3,05; 12,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,92</t>
+          <t>1,16; 10,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,39</t>
+          <t>0,63; 5,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,34</t>
+          <t>0,48; 4,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,75</t>
+          <t>1,71; 7,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,41</t>
+          <t>0,46; 4,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,22</t>
+          <t>2,69; 10,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,46</t>
+          <t>0,71; 3,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,11</t>
+          <t>0,23; 2,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,81</t>
+          <t>2,71; 7,54</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,36</t>
+          <t>0,67; 4,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,27 +1707,27 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,46</t>
+          <t>0,34; 3,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,43</t>
+          <t>1,18; 5,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,62</t>
+          <t>0,76; 4,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,63</t>
+          <t>1,03; 3,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,01</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,2</t>
+          <t>0,82; 2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,91; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,8</t>
+          <t>0,59; 1,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,23</t>
+          <t>0,76; 2,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,93</t>
+          <t>0,67; 2,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,69</t>
+          <t>1,55; 3,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,2</t>
+          <t>0,82; 2,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,45</t>
+          <t>0,75; 2,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,95</t>
+          <t>0,88; 1,84</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,41; 2,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,78</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,99</t>
+          <t>0,91; 2,05</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 4010</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>719; 6271</t>
+          <t>826; 6830</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 5010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 4273</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 4220</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1308; 7781</t>
+          <t>1354; 8328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>483; 4988</t>
+          <t>500; 5145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5439</t>
+          <t>0; 5050</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3154</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>631; 6305</t>
+          <t>635; 6287</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 2834</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4910</t>
+          <t>0; 5137</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>651; 6265</t>
+          <t>654; 6134</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>623; 5167</t>
+          <t>619; 5113</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1256; 7033</t>
+          <t>1251; 6992</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2734</t>
+          <t>0; 3012</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>867; 6957</t>
+          <t>668; 6657</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1900; 8841</t>
+          <t>1863; 8245</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1279; 7661</t>
+          <t>1868; 8721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>361; 5360</t>
+          <t>326; 5084</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4945</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3469</t>
+          <t>0; 3126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>643; 5430</t>
+          <t>645; 5767</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1358; 7734</t>
+          <t>1327; 7688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3046</t>
+          <t>0; 3636</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>520; 5167</t>
+          <t>520; 5425</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,27 +2843,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>0; 3428</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6119</t>
+          <t>0; 5607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4590</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>627; 5871</t>
+          <t>633; 5500</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>859; 6733</t>
+          <t>826; 6956</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>635; 5961</t>
+          <t>629; 6538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5302</t>
+          <t>0; 4111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5516</t>
+          <t>0; 6001</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>603; 5069</t>
+          <t>602; 4480</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 3549</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4263</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 3710</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2357; 9433</t>
+          <t>2188; 9754</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>624; 5966</t>
+          <t>632; 6031</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2417; 10861</t>
+          <t>2748; 11042</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4387</t>
+          <t>0; 3620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3249,17 +3249,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3909</t>
+          <t>0; 4029</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3908</t>
+          <t>0; 4333</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3107</t>
+          <t>0; 3428</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>712; 5976</t>
+          <t>699; 6063</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5538</t>
+          <t>0; 3837</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3076</t>
+          <t>0; 3112</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3546</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>777; 7431</t>
+          <t>733; 6945</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 3981</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3372</t>
+          <t>0; 3621</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>667; 6016</t>
+          <t>665; 6661</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 3908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2142; 9645</t>
+          <t>2135; 9611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3420</t>
+          <t>0; 3739</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>660; 6420</t>
+          <t>666; 6772</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3739; 17505</t>
+          <t>4202; 16544</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5282</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2038; 9839</t>
+          <t>2011; 9777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>652; 5952</t>
+          <t>652; 6361</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7563; 21901</t>
+          <t>7589; 21152</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>765; 6891</t>
+          <t>1051; 6991</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,27 +3675,27 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>600; 5678</t>
+          <t>564; 5532</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4720</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1416; 8914</t>
+          <t>1929; 8601</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3934</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1247; 7885</t>
+          <t>1294; 7581</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3668; 11692</t>
+          <t>3303; 12652</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3850</t>
+          <t>0; 3790</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2629; 10072</t>
+          <t>2598; 10567</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5013</t>
+          <t>0; 4887</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4955; 14993</t>
+          <t>5571; 15385</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5958; 17024</t>
+          <t>6422; 17518</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3992; 12658</t>
+          <t>4151; 13589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4649; 14870</t>
+          <t>5037; 15481</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4393; 13975</t>
+          <t>4825; 14763</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12635; 27606</t>
+          <t>11606; 26197</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5957; 16412</t>
+          <t>6091; 16307</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5837; 18656</t>
+          <t>5675; 19366</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11998; 27440</t>
+          <t>12396; 25768</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21118; 38755</t>
+          <t>20506; 37721</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12131; 25866</t>
+          <t>11636; 25341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11584; 28318</t>
+          <t>12932; 29264</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,95%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 12,89</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,29</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,42</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,36; 11,96</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,04</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,24</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,63</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,32</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,32</t>
+          <t>1,23; 7,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,22</t>
+          <t>0,41; 4,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,59; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,0</t>
+          <t>0,55; 4,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>1,15; 5,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,64</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,6</t>
+          <t>0,6; 5,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,34</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,17</t>
+          <t>0,32; 3,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,82</t>
+          <t>0,91; 4,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,07</t>
+          <t>0,6; 3,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,01</t>
+          <t>0,14; 2,26</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,92; 7,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,17</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,93</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,48</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,54</t>
+          <t>0,97; 5,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,25</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,76; 7,12</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,87</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,99</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,7; 7,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,52</t>
+          <t>0,51; 4,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,09</t>
+          <t>0,4; 3,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,7</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>4,7; 21,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,37 +1297,37 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>1,45; 10,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 21,16</t>
+          <t>0,0; 9,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,23</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,96</t>
+          <t>0,73; 7,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 12,27</t>
+          <t>3,25; 12,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>1,17; 10,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,03</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,36</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,62</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,77</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 10,06</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,65</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,54</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,65; 5,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,8</t>
+          <t>0,46; 4,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,72</t>
+          <t>2,45; 10,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,65</t>
+          <t>0,48; 4,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,6</t>
+          <t>1,67; 7,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,44</t>
+          <t>0,71; 3,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,26</t>
+          <t>0,23; 2,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,54</t>
+          <t>2,93; 8,07</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1697,57 +1697,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,43</t>
+          <t>0,85; 4,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,63</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0,8; 4,5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 3,37</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,31</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,24</t>
+          <t>0,66; 4,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,44</t>
+          <t>0,34; 3,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,93</t>
+          <t>1,18; 3,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,76; 3,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,26</t>
+          <t>0,58; 2,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,48</t>
+          <t>1,52; 3,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,93</t>
+          <t>0,81; 2,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,33</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,04</t>
+          <t>0,76; 2,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,5</t>
+          <t>0,91; 2,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,19</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,54</t>
+          <t>0,72; 2,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,84</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,59</t>
+          <t>1,45; 2,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,85; 1,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,05</t>
+          <t>0,89; 2,05</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,44 +2141,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>707</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1088</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>707</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>737</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4010</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>826; 6830</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 4346</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 4678</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2852</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>721; 6332</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3468</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5010</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4273</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4220</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3541</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1354; 8328</t>
+          <t>1393; 8614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>500; 5145</t>
+          <t>496; 5257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5050</t>
+          <t>0; 3661</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2527</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2190</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1910</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3199</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>870</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1467</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>645; 6048</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635; 6287</t>
+          <t>616; 5144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2834</t>
+          <t>1267; 6523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5137</t>
+          <t>0; 2297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>654; 6134</t>
+          <t>0; 3355</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>619; 5113</t>
+          <t>626; 6010</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1251; 6992</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>0; 4451</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>668; 6657</t>
+          <t>670; 7385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1863; 8245</t>
+          <t>1961; 8906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1868; 8721</t>
+          <t>1278; 7767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>326; 5084</t>
+          <t>291; 4869</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2562,44 +2562,44 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>694</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>3454</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>623</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>649; 5468</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3508</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>645; 5767</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>0; 3297</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3101</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1327; 7688</t>
+          <t>1344; 7805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3776</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3636</t>
+          <t>0; 3491</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,54 +2765,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1926</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>757</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2147</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>1382</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1105</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>520; 5425</t>
+          <t>0; 4067</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>624; 5855</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3145</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3428</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5607</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4590</t>
+          <t>521; 5796</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>633; 5500</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 3616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4609</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>826; 6956</t>
+          <t>790; 7081</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>629; 6538</t>
+          <t>637; 5760</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 4470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 6001</t>
+          <t>0; 5631</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,37 +2973,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5094</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1875</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>875</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>891</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>602; 4480</t>
+          <t>0; 2928</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>2167; 9988</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4487</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>609; 4505</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2188; 9754</t>
+          <t>0; 4359</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>0; 4445</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>632; 6031</t>
+          <t>634; 6097</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2748; 11042</t>
+          <t>2922; 11121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3620</t>
+          <t>0; 4376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,44 +3181,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>709</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>479</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>703; 6031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 4198</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0; 2462</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3562</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3706</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3673</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>699; 6063</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3837</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3112</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 3221</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>733; 6945</t>
+          <t>750; 6816</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4270</t>
+          <t>0; 4558</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 2779</t>
         </is>
       </c>
     </row>
@@ -3326,32 +3326,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2299</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8062</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2299</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12696</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3621</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>665; 6661</t>
+          <t>675; 6060</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3908</t>
+          <t>0; 4520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2135; 9611</t>
+          <t>3468; 14321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3739</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>666; 6772</t>
+          <t>662; 5901</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 3846</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4202; 16544</t>
+          <t>2050; 9314</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4413</t>
+          <t>0; 5064</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2011; 9777</t>
+          <t>2026; 10063</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>652; 6361</t>
+          <t>649; 6005</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7589; 21152</t>
+          <t>7734; 21292</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,54 +3597,54 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3072</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2279</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4066</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7138</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>1253</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>7138</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
           <t>5660</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1397</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1051; 6991</t>
+          <t>1397; 8161</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>0; 4505</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1369; 7682</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>564; 5532</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>0; 4357</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1929; 8601</t>
+          <t>1049; 7002</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4326</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1294; 7581</t>
+          <t>564; 5737</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4875</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3303; 12652</t>
+          <t>3784; 12423</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3790</t>
+          <t>0; 4386</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2598; 10567</t>
+          <t>2544; 10541</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 5062</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5571; 15385</t>
+          <t>4177; 15357</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6422; 17518</t>
+          <t>11363; 25718</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4151; 13589</t>
+          <t>6040; 16584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5037; 15481</t>
+          <t>5041; 17203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4825; 14763</t>
+          <t>5199; 14993</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11606; 26197</t>
+          <t>6421; 17680</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6091; 16307</t>
+          <t>3827; 12962</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5675; 19366</t>
+          <t>4524; 15265</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12396; 25768</t>
+          <t>12002; 25622</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20506; 37721</t>
+          <t>21163; 38840</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11636; 25341</t>
+          <t>12253; 25723</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12932; 29264</t>
+          <t>11820; 27210</t>
         </is>
       </c>
     </row>
